--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3680-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3680-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2AFD26B-E8F0-454F-8FA6-34751387914B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A1B472BE-A64E-4E71-B343-FBDC2881F465}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{351BE90F-B7F7-4C90-94D5-9EA1580654A7}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{63E6F166-3B4D-4853-BAD9-4EACB08EC323}"/>
   </bookViews>
   <sheets>
     <sheet name="3680-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1502,30 +1502,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A7710E8-A7F6-4957-95C7-531D4EB6CF21}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E81F86A-3EB6-49F5-AC4C-581AA99F6CC1}">
   <dimension ref="A1:X36"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="9" width="6.75" customWidth="1"/>
-    <col min="10" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="9" width="5.88671875" customWidth="1"/>
+    <col min="10" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1559,7 +1559,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1595,7 +1595,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1715,7 +1715,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1933,7 +1933,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2007,7 +2007,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2081,7 +2081,7 @@
         <v>1.0900000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>2.52</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2227,7 +2227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2301,7 +2301,7 @@
         <v>1.52</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2447,7 +2447,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2521,7 +2521,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2667,7 +2667,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2741,7 +2741,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2887,7 +2887,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2019</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>2.2799999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3107,7 +3107,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2018</v>
       </c>
@@ -3253,7 +3253,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2017</v>
       </c>
@@ -3325,7 +3325,7 @@
         <v>0.94</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2016</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>1.22</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2015</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2014</v>
       </c>
@@ -3541,7 +3541,7 @@
         <v>2.0699999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2013</v>
       </c>
@@ -3613,7 +3613,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2012</v>
       </c>
@@ -3685,7 +3685,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2011</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>6.12</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2010</v>
       </c>
@@ -3829,7 +3829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2009</v>
       </c>
@@ -3901,7 +3901,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2008</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35" t="s">
         <v>55</v>
       </c>
